--- a/artfynd/A 32618-2024 artfynd.xlsx
+++ b/artfynd/A 32618-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121641289</v>
       </c>
       <c r="B2" t="n">
-        <v>82393</v>
+        <v>82400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121641286</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 32618-2024 artfynd.xlsx
+++ b/artfynd/A 32618-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641289</v>
+        <v>121641286</v>
       </c>
       <c r="B2" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704926</v>
+        <v>704943</v>
       </c>
       <c r="R2" t="n">
-        <v>7207989</v>
+        <v>7207992</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641286</v>
+        <v>121641289</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704943</v>
+        <v>704926</v>
       </c>
       <c r="R3" t="n">
-        <v>7207992</v>
+        <v>7207989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32618-2024 artfynd.xlsx
+++ b/artfynd/A 32618-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641286</v>
+        <v>121641289</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704943</v>
+        <v>704926</v>
       </c>
       <c r="R2" t="n">
-        <v>7207992</v>
+        <v>7207989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641289</v>
+        <v>121641286</v>
       </c>
       <c r="B3" t="n">
-        <v>82417</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704926</v>
+        <v>704943</v>
       </c>
       <c r="R3" t="n">
-        <v>7207989</v>
+        <v>7207992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
